--- a/임시반편성_익명화.xlsx
+++ b/임시반편성_익명화.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -483,7 +483,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -630,7 +630,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -672,7 +672,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -798,7 +798,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -924,7 +924,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F191" t="n">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="F194" t="n">
